--- a/salidas/empresas/LIN.xlsx
+++ b/salidas/empresas/LIN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>35.67366409301758</v>
+        <v>35.67365264892578</v>
       </c>
       <c r="C2" t="n">
         <v>52.68000030517578</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>36.55398941040039</v>
+        <v>36.55399703979492</v>
       </c>
       <c r="C3" t="n">
         <v>53.97999954223633</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>37.51774215698242</v>
+        <v>37.51774978637695</v>
       </c>
       <c r="C4" t="n">
         <v>55.15000152587891</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>38.18444061279297</v>
+        <v>38.18444442749023</v>
       </c>
       <c r="C5" t="n">
         <v>56.13000106811523</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>35.85105514526367</v>
+        <v>35.8510627746582</v>
       </c>
       <c r="C6" t="n">
         <v>52.70000076293945</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>36.9021110534668</v>
+        <v>36.90210342407227</v>
       </c>
       <c r="C7" t="n">
         <v>54</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>37.47611999511719</v>
+        <v>37.47613525390625</v>
       </c>
       <c r="C8" t="n">
         <v>54.84000015258789</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>39.23240661621094</v>
+        <v>39.23241424560547</v>
       </c>
       <c r="C9" t="n">
         <v>57.40999984741211</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.60361099243164</v>
+        <v>40.60362243652344</v>
       </c>
       <c r="C10" t="n">
         <v>59.15999984741211</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>41.35172653198242</v>
+        <v>41.35173034667969</v>
       </c>
       <c r="C11" t="n">
         <v>60.25</v>
@@ -672,11 +684,11 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>42.82734680175781</v>
+        <v>42.82735061645508</v>
       </c>
       <c r="C12" t="n">
         <v>62.40000152587891</v>
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.88279342651367</v>
+        <v>40.88278961181641</v>
       </c>
       <c r="C13" t="n">
         <v>59.33000183105469</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>43.45303726196289</v>
+        <v>43.45302963256836</v>
       </c>
       <c r="C14" t="n">
         <v>63.06000137329102</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>42.50901031494141</v>
+        <v>42.50899887084961</v>
       </c>
       <c r="C15" t="n">
         <v>61.68999862670898</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>43.60011291503906</v>
+        <v>43.60012054443359</v>
       </c>
       <c r="C16" t="n">
         <v>62.95999908447266</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>44.70121002197266</v>
+        <v>44.70120239257812</v>
       </c>
       <c r="C17" t="n">
         <v>64.55000305175781</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>47.15264129638672</v>
+        <v>47.15266418457031</v>
       </c>
       <c r="C18" t="n">
         <v>68.08999633789062</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>50.07002639770508</v>
+        <v>50.07001495361328</v>
       </c>
       <c r="C19" t="n">
         <v>71.98999786376953</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>53.29027938842773</v>
+        <v>53.29027557373047</v>
       </c>
       <c r="C20" t="n">
         <v>76.62000274658203</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>52.6225700378418</v>
+        <v>52.62256240844727</v>
       </c>
       <c r="C21" t="n">
         <v>75.66000366210938</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>58.48826599121094</v>
+        <v>58.48827743530273</v>
       </c>
       <c r="C22" t="n">
         <v>83.76000213623047</v>
@@ -881,11 +893,11 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>59.6893424987793</v>
+        <v>59.68934631347656</v>
       </c>
       <c r="C23" t="n">
         <v>85.48000335693359</v>
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>59.61951446533203</v>
+        <v>59.61949157714844</v>
       </c>
       <c r="C24" t="n">
         <v>85.37999725341797</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>62.16390609741211</v>
+        <v>62.16388702392578</v>
       </c>
       <c r="C25" t="n">
         <v>88.70999908447266</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>56.55085372924805</v>
+        <v>56.55085754394531</v>
       </c>
       <c r="C26" t="n">
         <v>80.69999694824219</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>56.25652694702148</v>
+        <v>56.25653076171875</v>
       </c>
       <c r="C27" t="n">
         <v>80.27999877929688</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>59.3031120300293</v>
+        <v>59.30306625366211</v>
       </c>
       <c r="C28" t="n">
         <v>84.23000335693359</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>64.28785705566406</v>
+        <v>64.28783416748047</v>
       </c>
       <c r="C29" t="n">
         <v>91.30999755859375</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>66.92807769775391</v>
+        <v>66.9281005859375</v>
       </c>
       <c r="C30" t="n">
         <v>95.05999755859375</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>66.61247253417969</v>
+        <v>66.61248016357422</v>
       </c>
       <c r="C31" t="n">
         <v>94.23999786376953</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>66.25199890136719</v>
+        <v>66.25205230712891</v>
       </c>
       <c r="C32" t="n">
         <v>93.73000335693359</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>63.50239181518555</v>
+        <v>63.50240325927734</v>
       </c>
       <c r="C33" t="n">
         <v>89.83999633789062</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>50.92345428466797</v>
+        <v>50.92344284057617</v>
       </c>
       <c r="C34" t="n">
         <v>71.73999786376953</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>46.24566650390625</v>
+        <v>46.24563980102539</v>
       </c>
       <c r="C35" t="n">
         <v>65.15000152587891</v>
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>42.42401885986328</v>
+        <v>42.42402267456055</v>
       </c>
       <c r="C37" t="n">
         <v>59.36000061035156</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>44.49661636352539</v>
+        <v>44.49662017822266</v>
       </c>
       <c r="C38" t="n">
         <v>62.2599983215332</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>40.55867767333984</v>
+        <v>40.55868911743164</v>
       </c>
       <c r="C39" t="n">
         <v>56.75</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>48.44216918945312</v>
+        <v>48.44217300415039</v>
       </c>
       <c r="C40" t="n">
         <v>67.29000091552734</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>53.71184158325195</v>
+        <v>53.71185302734375</v>
       </c>
       <c r="C41" t="n">
         <v>74.61000061035156</v>
@@ -1248,11 +1260,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>52.69678497314453</v>
+        <v>52.69676971435547</v>
       </c>
       <c r="C42" t="n">
         <v>73.19999694824219</v>
@@ -1273,11 +1285,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>51.43135452270508</v>
+        <v>51.4313850402832</v>
       </c>
       <c r="C43" t="n">
         <v>71.06999969482422</v>
@@ -1298,11 +1310,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>56.57668685913086</v>
+        <v>56.57667922973633</v>
       </c>
       <c r="C44" t="n">
         <v>78.18000030517578</v>
@@ -1323,11 +1335,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>55.4477424621582</v>
+        <v>55.44776916503906</v>
       </c>
       <c r="C45" t="n">
         <v>76.62000274658203</v>
@@ -1348,7 +1360,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1373,11 +1385,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>57.79485321044922</v>
+        <v>57.7948112487793</v>
       </c>
       <c r="C47" t="n">
         <v>79.44000244140625</v>
@@ -1398,11 +1410,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>59.67913436889648</v>
+        <v>59.67911148071289</v>
       </c>
       <c r="C48" t="n">
         <v>82.02999877929688</v>
@@ -1423,11 +1435,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>58.71168899536133</v>
+        <v>58.71167755126953</v>
       </c>
       <c r="C49" t="n">
         <v>80.30999755859375</v>
@@ -1448,11 +1460,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>55.06368255615234</v>
+        <v>55.06367492675781</v>
       </c>
       <c r="C50" t="n">
         <v>75.31999969482422</v>
@@ -1473,11 +1485,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>54.93210220336914</v>
+        <v>54.93207168579102</v>
       </c>
       <c r="C51" t="n">
         <v>75.13999938964844</v>
@@ -1502,11 +1514,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>61.03506851196289</v>
+        <v>61.03508377075195</v>
       </c>
       <c r="C52" t="n">
         <v>83</v>
@@ -1531,11 +1543,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>61.60129165649414</v>
+        <v>61.60128021240234</v>
       </c>
       <c r="C53" t="n">
         <v>83.76999664306641</v>
@@ -1560,11 +1572,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>57.0640983581543</v>
+        <v>57.06410980224609</v>
       </c>
       <c r="C54" t="n">
         <v>77.59999847412109</v>
@@ -1589,11 +1601,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>56.20428085327148</v>
+        <v>56.20429229736328</v>
       </c>
       <c r="C55" t="n">
         <v>75.98999786376953</v>
@@ -1618,11 +1630,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>64.21442413330078</v>
+        <v>64.21440124511719</v>
       </c>
       <c r="C56" t="n">
         <v>86.81999969482422</v>
@@ -1647,11 +1659,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>63.6301155090332</v>
+        <v>63.63013458251953</v>
       </c>
       <c r="C57" t="n">
         <v>86.02999877929688</v>
@@ -1676,7 +1688,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1705,11 +1717,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>67.90839385986328</v>
+        <v>67.90838623046875</v>
       </c>
       <c r="C59" t="n">
         <v>91.33999633789062</v>
@@ -1734,11 +1746,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>68.43624877929688</v>
+        <v>68.43627166748047</v>
       </c>
       <c r="C60" t="n">
         <v>92.05000305175781</v>
@@ -1763,11 +1775,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>71.31879425048828</v>
+        <v>71.31880187988281</v>
       </c>
       <c r="C61" t="n">
         <v>95.47000122070312</v>
@@ -1792,11 +1804,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>69.5035400390625</v>
+        <v>69.50351715087891</v>
       </c>
       <c r="C62" t="n">
         <v>93.04000091552734</v>
@@ -1821,11 +1833,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>74.23965454101562</v>
+        <v>74.23967742919922</v>
       </c>
       <c r="C63" t="n">
         <v>99.37999725341797</v>
@@ -1850,11 +1862,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>76.28739166259766</v>
+        <v>76.28736877441406</v>
       </c>
       <c r="C64" t="n">
         <v>101.5999984741211</v>
@@ -1879,11 +1891,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>79.90653991699219</v>
+        <v>79.90652465820312</v>
       </c>
       <c r="C65" t="n">
         <v>106.4199981689453</v>
@@ -1908,11 +1920,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>79.47103118896484</v>
+        <v>79.47103881835938</v>
       </c>
       <c r="C66" t="n">
         <v>105.8399963378906</v>
@@ -1937,11 +1949,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>81.78214263916016</v>
+        <v>81.78216552734375</v>
       </c>
       <c r="C67" t="n">
         <v>108.3899993896484</v>
@@ -1966,11 +1978,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>78.19816589355469</v>
+        <v>78.19817352294922</v>
       </c>
       <c r="C68" t="n">
         <v>103.6399993896484</v>
@@ -1995,11 +2007,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>74.31243896484375</v>
+        <v>74.31242370605469</v>
       </c>
       <c r="C69" t="n">
         <v>98.48999786376953</v>
@@ -2024,11 +2036,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>70.89328002929688</v>
+        <v>70.89331817626953</v>
       </c>
       <c r="C70" t="n">
         <v>93.48000335693359</v>
@@ -2053,11 +2065,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>77.10440063476562</v>
+        <v>77.10443115234375</v>
       </c>
       <c r="C71" t="n">
         <v>101.6699981689453</v>
@@ -2082,11 +2094,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>77.35469055175781</v>
+        <v>77.35469818115234</v>
       </c>
       <c r="C72" t="n">
         <v>102</v>
@@ -2111,7 +2123,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2140,11 +2152,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>80.94274139404297</v>
+        <v>80.94271087646484</v>
       </c>
       <c r="C74" t="n">
         <v>106.1999969482422</v>
@@ -2169,7 +2181,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2198,11 +2210,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>87.81572723388672</v>
+        <v>87.81576538085938</v>
       </c>
       <c r="C76" t="n">
         <v>114.6399993896484</v>
@@ -2227,11 +2239,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>88.62771606445312</v>
+        <v>88.62770843505859</v>
       </c>
       <c r="C77" t="n">
         <v>115.6999969482422</v>
@@ -2256,7 +2268,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2285,11 +2297,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>83.73150634765625</v>
+        <v>83.73149871826172</v>
       </c>
       <c r="C79" t="n">
         <v>108.7300033569336</v>
@@ -2314,11 +2326,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>79.90419006347656</v>
+        <v>79.90415954589844</v>
       </c>
       <c r="C80" t="n">
         <v>103.7600021362305</v>
@@ -2343,11 +2355,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>81.24415588378906</v>
+        <v>81.24413299560547</v>
       </c>
       <c r="C81" t="n">
         <v>105.5</v>
@@ -2372,11 +2384,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>80.42096710205078</v>
+        <v>80.42095947265625</v>
       </c>
       <c r="C82" t="n">
         <v>103.879997253418</v>
@@ -2401,11 +2413,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>82.22478485107422</v>
+        <v>82.22475433349609</v>
       </c>
       <c r="C83" t="n">
         <v>106.2099990844727</v>
@@ -2430,11 +2442,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>82.99893951416016</v>
+        <v>82.99895477294922</v>
       </c>
       <c r="C84" t="n">
         <v>107.2099990844727</v>
@@ -2459,11 +2471,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>85.17625427246094</v>
+        <v>85.17626953125</v>
       </c>
       <c r="C85" t="n">
         <v>109.4499969482422</v>
@@ -2488,11 +2500,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>85.89222717285156</v>
+        <v>85.89223480224609</v>
       </c>
       <c r="C86" t="n">
         <v>110.370002746582</v>
@@ -2517,11 +2529,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>87.97785949707031</v>
+        <v>87.97786712646484</v>
       </c>
       <c r="C87" t="n">
         <v>113.0500030517578</v>
@@ -2546,7 +2558,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2575,11 +2587,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>89.42584228515625</v>
+        <v>89.42587280273438</v>
       </c>
       <c r="C89" t="n">
         <v>114.3000030517578</v>
@@ -2604,11 +2616,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>89.4493408203125</v>
+        <v>89.44934844970703</v>
       </c>
       <c r="C90" t="n">
         <v>114.3300018310547</v>
@@ -2633,11 +2645,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>90.56447601318359</v>
+        <v>90.56449890136719</v>
       </c>
       <c r="C91" t="n">
         <v>115.1600036621094</v>
@@ -2662,11 +2674,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>94.50448608398438</v>
+        <v>94.50447845458984</v>
       </c>
       <c r="C92" t="n">
         <v>120.1699981689453</v>
@@ -2691,7 +2703,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2720,11 +2732,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>95.02125549316406</v>
+        <v>95.02129364013672</v>
       </c>
       <c r="C94" t="n">
         <v>120.2099990844727</v>
@@ -2749,11 +2761,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>98.57837677001953</v>
+        <v>98.57835388183594</v>
       </c>
       <c r="C95" t="n">
         <v>124.7099990844727</v>
@@ -2778,11 +2790,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>99.80355072021484</v>
+        <v>99.80355834960938</v>
       </c>
       <c r="C96" t="n">
         <v>126.2600021362305</v>
@@ -2807,11 +2819,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>103.2823791503906</v>
+        <v>103.2823715209961</v>
       </c>
       <c r="C97" t="n">
         <v>130.0299987792969</v>
@@ -2836,7 +2848,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2865,11 +2877,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>103.5524597167969</v>
+        <v>103.5524368286133</v>
       </c>
       <c r="C99" t="n">
         <v>130.3699951171875</v>
@@ -2894,11 +2906,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>104.5477828979492</v>
+        <v>104.5477676391602</v>
       </c>
       <c r="C100" t="n">
         <v>130.9700012207031</v>
@@ -2923,11 +2935,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>104.2125015258789</v>
+        <v>104.212516784668</v>
       </c>
       <c r="C101" t="n">
         <v>130.5500030517578</v>
@@ -2952,11 +2964,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>105.5615692138672</v>
+        <v>105.5615463256836</v>
       </c>
       <c r="C102" t="n">
         <v>132.2400054931641</v>
@@ -2981,11 +2993,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>106.5586700439453</v>
+        <v>106.5586395263672</v>
       </c>
       <c r="C103" t="n">
         <v>132.8399963378906</v>
@@ -3010,11 +3022,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>102.7885208129883</v>
+        <v>102.7884979248047</v>
       </c>
       <c r="C104" t="n">
         <v>128.1399993896484</v>
@@ -3039,11 +3051,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>105.5238876342773</v>
+        <v>105.5238723754883</v>
       </c>
       <c r="C105" t="n">
         <v>131.5500030517578</v>
@@ -3068,11 +3080,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>103.9895248413086</v>
+        <v>103.9895401000977</v>
       </c>
       <c r="C106" t="n">
         <v>129</v>
@@ -3097,11 +3109,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>101.5631408691406</v>
+        <v>101.563117980957</v>
       </c>
       <c r="C107" t="n">
         <v>125.9899978637695</v>
@@ -3126,11 +3138,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>103.48974609375</v>
+        <v>103.4897308349609</v>
       </c>
       <c r="C108" t="n">
         <v>128.3800048828125</v>
@@ -3155,11 +3167,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>104.9721374511719</v>
+        <v>104.9721603393555</v>
       </c>
       <c r="C109" t="n">
         <v>129.5599975585938</v>
@@ -3184,11 +3196,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>97.7044677734375</v>
+        <v>97.70446014404297</v>
       </c>
       <c r="C110" t="n">
         <v>120.5899963378906</v>
@@ -3213,11 +3225,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>103.6272048950195</v>
+        <v>103.6271896362305</v>
       </c>
       <c r="C111" t="n">
         <v>127.9000015258789</v>
@@ -3242,11 +3254,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>98.37103271484375</v>
+        <v>98.37107086181641</v>
       </c>
       <c r="C112" t="n">
         <v>120.7399978637695</v>
@@ -3271,11 +3283,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>99.34056854248047</v>
+        <v>99.34059143066406</v>
       </c>
       <c r="C113" t="n">
         <v>121.9300003051758</v>
@@ -3300,11 +3312,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>100.098274230957</v>
+        <v>100.0982513427734</v>
       </c>
       <c r="C114" t="n">
         <v>122.8600006103516</v>
@@ -3329,11 +3341,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>97.97312927246094</v>
+        <v>97.97319030761719</v>
       </c>
       <c r="C115" t="n">
         <v>119.5500030517578</v>
@@ -3358,11 +3370,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>93.53958129882812</v>
+        <v>93.53959655761719</v>
       </c>
       <c r="C116" t="n">
         <v>114.1399993896484</v>
@@ -3387,7 +3399,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3416,11 +3428,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>84.05971527099609</v>
+        <v>84.05970764160156</v>
       </c>
       <c r="C118" t="n">
         <v>101.8600006103516</v>
@@ -3445,11 +3457,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>91.67674255371094</v>
+        <v>91.67676544189453</v>
       </c>
       <c r="C119" t="n">
         <v>111.0899963378906</v>
@@ -3474,11 +3486,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>93.08792877197266</v>
+        <v>93.08793640136719</v>
       </c>
       <c r="C120" t="n">
         <v>112.8000030517578</v>
@@ -3503,11 +3515,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>85.056396484375</v>
+        <v>85.05638885498047</v>
       </c>
       <c r="C121" t="n">
         <v>102.4000015258789</v>
@@ -3532,7 +3544,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3561,11 +3573,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>84.54974365234375</v>
+        <v>84.54975128173828</v>
       </c>
       <c r="C123" t="n">
         <v>101.7900009155273</v>
@@ -3590,11 +3602,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>95.75510406494141</v>
+        <v>95.75513458251953</v>
       </c>
       <c r="C124" t="n">
         <v>114.4499969482422</v>
@@ -3619,11 +3631,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>98.27344512939453</v>
+        <v>98.27346038818359</v>
       </c>
       <c r="C125" t="n">
         <v>117.4599990844727</v>
@@ -3648,11 +3660,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>91.91486358642578</v>
+        <v>91.91485595703125</v>
       </c>
       <c r="C126" t="n">
         <v>109.8600006103516</v>
@@ -3677,11 +3689,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>94.67385864257812</v>
+        <v>94.67385101318359</v>
       </c>
       <c r="C127" t="n">
         <v>112.3899993896484</v>
@@ -3706,7 +3718,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3735,11 +3747,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>102.8027191162109</v>
+        <v>102.8026885986328</v>
       </c>
       <c r="C129" t="n">
         <v>122.0400009155273</v>
@@ -3764,11 +3776,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>102.4056167602539</v>
+        <v>102.4056396484375</v>
       </c>
       <c r="C130" t="n">
         <v>120.8300018310547</v>
@@ -3793,11 +3805,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>99.21050262451172</v>
+        <v>99.21047973632812</v>
       </c>
       <c r="C131" t="n">
         <v>117.0599975585938</v>
@@ -3822,11 +3834,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>101.9564743041992</v>
+        <v>101.9564437866211</v>
       </c>
       <c r="C132" t="n">
         <v>120.3000030517578</v>
@@ -3851,11 +3863,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>99.94754791259766</v>
+        <v>99.947509765625</v>
       </c>
       <c r="C133" t="n">
         <v>117.1900024414062</v>
@@ -3880,11 +3892,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>101.0136032104492</v>
+        <v>101.0136337280273</v>
       </c>
       <c r="C134" t="n">
         <v>118.4400024414062</v>
@@ -3909,11 +3921,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>101.2438812255859</v>
+        <v>101.2438735961914</v>
       </c>
       <c r="C135" t="n">
         <v>118.7099990844727</v>
@@ -3938,11 +3950,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>101.8256149291992</v>
+        <v>101.8255996704102</v>
       </c>
       <c r="C136" t="n">
         <v>118.5999984741211</v>
@@ -3967,11 +3979,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>107.3032150268555</v>
+        <v>107.3032379150391</v>
       </c>
       <c r="C137" t="n">
         <v>124.9800033569336</v>
@@ -3996,11 +4008,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>113.5793151855469</v>
+        <v>113.5793380737305</v>
       </c>
       <c r="C138" t="n">
         <v>132.2899932861328</v>
@@ -4025,11 +4037,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>114.462760925293</v>
+        <v>114.4627685546875</v>
       </c>
       <c r="C139" t="n">
         <v>132.5500030517578</v>
@@ -4054,11 +4066,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>112.3988952636719</v>
+        <v>112.3989028930664</v>
       </c>
       <c r="C140" t="n">
         <v>130.1600036621094</v>
@@ -4083,11 +4095,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>113.590576171875</v>
+        <v>113.5905685424805</v>
       </c>
       <c r="C141" t="n">
         <v>131.5399932861328</v>
@@ -4112,11 +4124,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>121.3976287841797</v>
+        <v>121.3975982666016</v>
       </c>
       <c r="C142" t="n">
         <v>139.7400054931641</v>
@@ -4141,7 +4153,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4170,11 +4182,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>133.7163238525391</v>
+        <v>133.7163391113281</v>
       </c>
       <c r="C144" t="n">
         <v>153.9199981689453</v>
@@ -4199,11 +4211,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>135.0718841552734</v>
+        <v>135.0718536376953</v>
       </c>
       <c r="C145" t="n">
         <v>154.6799926757812</v>
@@ -4228,11 +4240,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>141.0186157226562</v>
+        <v>141.0185546875</v>
       </c>
       <c r="C146" t="n">
         <v>161.4900054931641</v>
@@ -4257,11 +4269,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>130.7668762207031</v>
+        <v>130.766845703125</v>
       </c>
       <c r="C147" t="n">
         <v>149.75</v>
@@ -4286,11 +4298,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>126.6919860839844</v>
+        <v>126.692008972168</v>
       </c>
       <c r="C148" t="n">
         <v>144.3000030517578</v>
@@ -4315,11 +4327,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>133.9089508056641</v>
+        <v>133.908935546875</v>
       </c>
       <c r="C149" t="n">
         <v>152.5200042724609</v>
@@ -4344,11 +4356,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>137.1926116943359</v>
+        <v>137.1925659179688</v>
       </c>
       <c r="C150" t="n">
         <v>156.2599945068359</v>
@@ -4373,11 +4385,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>139.5738830566406</v>
+        <v>139.5738677978516</v>
       </c>
       <c r="C151" t="n">
         <v>158.1499938964844</v>
@@ -4402,11 +4414,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>147.8256225585938</v>
+        <v>147.8256378173828</v>
       </c>
       <c r="C152" t="n">
         <v>167.5</v>
@@ -4431,11 +4443,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>140.3153381347656</v>
+        <v>140.3153991699219</v>
       </c>
       <c r="C153" t="n">
         <v>158.1900024414062</v>
@@ -4460,7 +4472,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4489,11 +4501,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>146.7727508544922</v>
+        <v>146.7727661132812</v>
       </c>
       <c r="C155" t="n">
         <v>165.4700012207031</v>
@@ -4518,11 +4530,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>141.0781707763672</v>
+        <v>141.0782012939453</v>
       </c>
       <c r="C156" t="n">
         <v>159.0500030517578</v>
@@ -4547,11 +4559,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>139.1398010253906</v>
+        <v>139.1397857666016</v>
       </c>
       <c r="C157" t="n">
         <v>156.0399932861328</v>
@@ -4576,11 +4588,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>145.3548736572266</v>
+        <v>145.3548278808594</v>
       </c>
       <c r="C158" t="n">
         <v>163.0099945068359</v>
@@ -4605,11 +4617,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>154.4768981933594</v>
+        <v>154.4769134521484</v>
       </c>
       <c r="C159" t="n">
         <v>173.2400054931641</v>
@@ -4634,7 +4646,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4663,11 +4675,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>161.5724487304688</v>
+        <v>161.5724945068359</v>
       </c>
       <c r="C161" t="n">
         <v>180.2599945068359</v>
@@ -4692,11 +4704,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>162.6082153320312</v>
+        <v>162.608154296875</v>
       </c>
       <c r="C162" t="n">
         <v>180.5500030517578</v>
@@ -4721,11 +4733,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>180.8459167480469</v>
+        <v>180.8458709716797</v>
       </c>
       <c r="C163" t="n">
         <v>200.8000030517578</v>
@@ -4750,11 +4762,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>172.2719116210938</v>
+        <v>172.2719421386719</v>
       </c>
       <c r="C164" t="n">
         <v>191.2799987792969</v>
@@ -4779,7 +4791,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4808,11 +4820,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>175.2867584228516</v>
+        <v>175.2867736816406</v>
       </c>
       <c r="C166" t="n">
         <v>193.7200012207031</v>
@@ -4837,11 +4849,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>179.4762115478516</v>
+        <v>179.4762573242188</v>
       </c>
       <c r="C167" t="n">
         <v>198.3500061035156</v>
@@ -4866,11 +4878,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>186.5882720947266</v>
+        <v>186.5883178710938</v>
       </c>
       <c r="C168" t="n">
         <v>206.2100067138672</v>
@@ -4895,11 +4907,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>193.4626007080078</v>
+        <v>193.4626312255859</v>
       </c>
       <c r="C169" t="n">
         <v>212.8999938964844</v>
@@ -4924,11 +4936,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>184.5845947265625</v>
+        <v>184.5846405029297</v>
       </c>
       <c r="C170" t="n">
         <v>203.1300048828125</v>
@@ -4953,11 +4965,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>173.5711059570312</v>
+        <v>173.5711212158203</v>
       </c>
       <c r="C171" t="n">
         <v>191.0099945068359</v>
@@ -4982,7 +4994,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -5011,11 +5023,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>167.9790802001953</v>
+        <v>167.9791107177734</v>
       </c>
       <c r="C173" t="n">
         <v>183.9900054931641</v>
@@ -5040,11 +5052,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>184.7322692871094</v>
+        <v>184.7322998046875</v>
       </c>
       <c r="C174" t="n">
         <v>202.3399963378906</v>
@@ -5069,11 +5081,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>194.5651245117188</v>
+        <v>194.5650939941406</v>
       </c>
       <c r="C175" t="n">
         <v>212.1100006103516</v>
@@ -5098,11 +5110,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>224.83544921875</v>
+        <v>224.8354949951172</v>
       </c>
       <c r="C176" t="n">
         <v>245.1100006103516</v>
@@ -5127,11 +5139,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>229.0824890136719</v>
+        <v>229.0825042724609</v>
       </c>
       <c r="C177" t="n">
         <v>249.7400054931641</v>
@@ -5156,11 +5168,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>219.2545471191406</v>
+        <v>219.2545776367188</v>
       </c>
       <c r="C178" t="n">
         <v>238.1300048828125</v>
@@ -5185,11 +5197,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>202.8746948242188</v>
+        <v>202.8746795654297</v>
       </c>
       <c r="C179" t="n">
         <v>220.3399963378906</v>
@@ -5214,11 +5226,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>236.0948333740234</v>
+        <v>236.0948181152344</v>
       </c>
       <c r="C180" t="n">
         <v>256.4200134277344</v>
@@ -5243,11 +5255,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>243.5286560058594</v>
+        <v>243.5286254882812</v>
       </c>
       <c r="C181" t="n">
         <v>263.510009765625</v>
@@ -5272,11 +5284,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>226.7918701171875</v>
+        <v>226.7919158935547</v>
       </c>
       <c r="C182" t="n">
         <v>245.3999938964844</v>
@@ -5301,11 +5313,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>225.7475433349609</v>
+        <v>225.7475738525391</v>
       </c>
       <c r="C183" t="n">
         <v>244.2700042724609</v>
@@ -5330,7 +5342,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5359,11 +5371,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>265.3013916015625</v>
+        <v>265.3014221191406</v>
       </c>
       <c r="C185" t="n">
         <v>285.8399963378906</v>
@@ -5388,11 +5400,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>279.0008850097656</v>
+        <v>279.0008239746094</v>
       </c>
       <c r="C186" t="n">
         <v>300.6000061035156</v>
@@ -5417,11 +5429,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>269.271484375</v>
+        <v>269.2714538574219</v>
       </c>
       <c r="C187" t="n">
         <v>289.1000061035156</v>
@@ -5446,7 +5458,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5475,7 +5487,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5504,11 +5516,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>274.1838073730469</v>
+        <v>274.1838684082031</v>
       </c>
       <c r="C190" t="n">
         <v>293.3800048828125</v>
@@ -5533,11 +5545,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>298.314453125</v>
+        <v>298.3144226074219</v>
       </c>
       <c r="C191" t="n">
         <v>319.2000122070312</v>
@@ -5562,11 +5574,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>297.3238220214844</v>
+        <v>297.3237915039062</v>
       </c>
       <c r="C192" t="n">
         <v>318.1400146484375</v>
@@ -5591,11 +5603,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>324.8445129394531</v>
+        <v>324.8446044921875</v>
       </c>
       <c r="C193" t="n">
         <v>346.4299926757812</v>
@@ -5620,11 +5632,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>298.8236389160156</v>
+        <v>298.8235778808594</v>
       </c>
       <c r="C194" t="n">
         <v>318.6799926757812</v>
@@ -5649,11 +5661,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>274.9687194824219</v>
+        <v>274.9687805175781</v>
       </c>
       <c r="C195" t="n">
         <v>293.239990234375</v>
@@ -5678,7 +5690,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5707,11 +5719,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>293.6961364746094</v>
+        <v>293.6960754394531</v>
       </c>
       <c r="C197" t="n">
         <v>311.9599914550781</v>
@@ -5736,11 +5748,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>305.6713256835938</v>
+        <v>305.6712951660156</v>
       </c>
       <c r="C198" t="n">
         <v>324.6799926757812</v>
@@ -5765,11 +5777,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>271.69091796875</v>
+        <v>271.6908569335938</v>
       </c>
       <c r="C199" t="n">
         <v>287.5299987792969</v>
@@ -5794,7 +5806,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5823,11 +5835,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>267.2782287597656</v>
+        <v>267.2781677246094</v>
       </c>
       <c r="C201" t="n">
         <v>282.8599853515625</v>
@@ -5852,11 +5864,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>255.7972564697266</v>
+        <v>255.7971343994141</v>
       </c>
       <c r="C202" t="n">
         <v>269.5899963378906</v>
@@ -5881,11 +5893,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>282.136962890625</v>
+        <v>282.1369934082031</v>
       </c>
       <c r="C203" t="n">
         <v>297.3500061035156</v>
@@ -5910,11 +5922,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>319.2650146484375</v>
+        <v>319.2649841308594</v>
       </c>
       <c r="C204" t="n">
         <v>336.4800109863281</v>
@@ -5939,11 +5951,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>310.5718383789062</v>
+        <v>310.5719299316406</v>
       </c>
       <c r="C205" t="n">
         <v>326.1799926757812</v>
@@ -5968,7 +5980,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5997,11 +6009,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>331.7000427246094</v>
+        <v>331.7000732421875</v>
       </c>
       <c r="C207" t="n">
         <v>348.3699951171875</v>
@@ -6026,7 +6038,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -6055,11 +6067,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>353.0894775390625</v>
+        <v>353.0894470214844</v>
       </c>
       <c r="C209" t="n">
         <v>369.4500122070312</v>
@@ -6084,11 +6096,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>337.9986877441406</v>
+        <v>337.9987182617188</v>
       </c>
       <c r="C210" t="n">
         <v>353.6600036621094</v>
@@ -6113,11 +6125,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>365.5221862792969</v>
+        <v>365.5222473144531</v>
       </c>
       <c r="C211" t="n">
         <v>381.0799865722656</v>
@@ -6142,11 +6154,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>374.7207336425781</v>
+        <v>374.7207641601562</v>
       </c>
       <c r="C212" t="n">
         <v>390.6700134277344</v>
@@ -6171,11 +6183,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>371.2389831542969</v>
+        <v>371.2389221191406</v>
       </c>
       <c r="C213" t="n">
         <v>387.0400085449219</v>
@@ -6200,11 +6212,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>358.3291015625</v>
+        <v>358.3290710449219</v>
       </c>
       <c r="C214" t="n">
         <v>372.3500061035156</v>
@@ -6229,11 +6241,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>367.7696838378906</v>
+        <v>367.7696533203125</v>
       </c>
       <c r="C215" t="n">
         <v>382.1600036621094</v>
@@ -6258,7 +6270,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6287,11 +6299,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>396.4662780761719</v>
+        <v>396.4662475585938</v>
       </c>
       <c r="C217" t="n">
         <v>410.7099914550781</v>
@@ -6316,11 +6328,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>390.790283203125</v>
+        <v>390.7901611328125</v>
       </c>
       <c r="C218" t="n">
         <v>404.8299865722656</v>
@@ -6345,7 +6357,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6374,7 +6386,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6403,11 +6415,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>426.9259033203125</v>
+        <v>426.9258117675781</v>
       </c>
       <c r="C221" t="n">
         <v>440.9599914550781</v>
@@ -6432,7 +6444,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6461,7 +6473,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6490,7 +6502,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6519,11 +6531,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>464.5157165527344</v>
+        <v>464.5156860351562</v>
       </c>
       <c r="C225" t="n">
         <v>478.25</v>
@@ -6548,11 +6560,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>464.5276489257812</v>
+        <v>464.5276794433594</v>
       </c>
       <c r="C226" t="n">
         <v>476.8599853515625</v>
@@ -6577,7 +6589,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6606,7 +6618,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6635,7 +6647,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6664,11 +6676,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>435.9007568359375</v>
+        <v>435.9006958007812</v>
       </c>
       <c r="C230" t="n">
         <v>446.1199951171875</v>
@@ -6693,7 +6705,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6722,7 +6734,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6751,11 +6763,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>444.3251037597656</v>
+        <v>444.3251342773438</v>
       </c>
       <c r="C233" t="n">
         <v>453.2300109863281</v>
@@ -6780,11 +6792,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>458.3931579589844</v>
+        <v>458.3931274414062</v>
       </c>
       <c r="C234" t="n">
         <v>467.5799865722656</v>
@@ -6809,11 +6821,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>461.4287109375</v>
+        <v>461.4286804199219</v>
       </c>
       <c r="C235" t="n">
         <v>469.1799926757812</v>
@@ -6838,7 +6850,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6867,7 +6879,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6896,7 +6908,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6925,11 +6937,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>412.701416015625</v>
+        <v>412.7014465332031</v>
       </c>
       <c r="C239" t="n">
         <v>418.2999877929688</v>
@@ -6954,7 +6966,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6983,11 +6995,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>422.2325134277344</v>
+        <v>422.2324829101562</v>
       </c>
       <c r="C241" t="n">
         <v>426.3900146484375</v>
@@ -7012,7 +7024,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -7041,7 +7053,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7070,7 +7082,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7099,7 +7111,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7128,7 +7140,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7157,7 +7169,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7186,7 +7198,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7215,7 +7227,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7244,32 +7256,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>469.7200012207031</v>
+        <v>468.1400146484375</v>
       </c>
       <c r="C250" t="n">
-        <v>469.7200012207031</v>
+        <v>468.1400146484375</v>
       </c>
       <c r="D250" t="n">
-        <v>32314700</v>
+        <v>34399100</v>
       </c>
       <c r="E250" t="n">
         <v>15.5</v>
       </c>
       <c r="F250" t="n">
-        <v>30.3045162077873</v>
+        <v>30.20258159022178</v>
       </c>
       <c r="G250" t="n">
         <v>460980163</v>
       </c>
       <c r="H250" t="n">
-        <v>216531602727.0799</v>
+        <v>215803260259.4591</v>
       </c>
       <c r="I250" t="n">
-        <v>0.07009997955161468</v>
+        <v>0.07462164917495592</v>
       </c>
     </row>
   </sheetData>
@@ -7301,75 +7313,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39448</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39538</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>39932</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7405,13 +7417,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7447,13 +7459,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7489,13 +7501,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39722</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39813</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7522,7 +7534,7 @@
       <c r="I5" t="n">
         <v>3.8</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="K5" t="n">
@@ -7535,13 +7547,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>39932</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7568,7 +7580,7 @@
       <c r="I6" t="n">
         <v>3.77</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="K6" t="n">
@@ -7581,13 +7593,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7614,7 +7626,7 @@
       <c r="I7" t="n">
         <v>3.649999999999999</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="K7" t="n">
@@ -7627,13 +7639,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7660,7 +7672,7 @@
       <c r="I8" t="n">
         <v>3.579999999999999</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="K8" t="n">
@@ -7673,13 +7685,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7706,7 +7718,7 @@
       <c r="I9" t="n">
         <v>4.01</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="K9" t="n">
@@ -7719,13 +7731,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7752,7 +7764,7 @@
       <c r="I10" t="n">
         <v>4.09</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="K10" t="n">
@@ -7765,13 +7777,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7798,7 +7810,7 @@
       <c r="I11" t="n">
         <v>4.319999999999999</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="K11" t="n">
@@ -7811,13 +7823,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7844,7 +7856,7 @@
       <c r="I12" t="n">
         <v>4.489999999999999</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="K12" t="n">
@@ -7857,13 +7869,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7890,7 +7902,7 @@
       <c r="I13" t="n">
         <v>3.84</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="K13" t="n">
@@ -7903,13 +7915,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7936,7 +7948,7 @@
       <c r="I14" t="n">
         <v>4.12</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="K14" t="n">
@@ -7949,13 +7961,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7982,7 +7994,7 @@
       <c r="I15" t="n">
         <v>4.31</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="K15" t="n">
@@ -7995,13 +8007,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -8028,7 +8040,7 @@
       <c r="I16" t="n">
         <v>4.5</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="K16" t="n">
@@ -8041,13 +8053,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8074,7 +8086,7 @@
       <c r="I17" t="n">
         <v>5.449999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="K17" t="n">
@@ -8087,13 +8099,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8120,7 +8132,7 @@
       <c r="I18" t="n">
         <v>5.539999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="K18" t="n">
@@ -8133,13 +8145,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8166,7 +8178,7 @@
       <c r="I19" t="n">
         <v>5.58</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="K19" t="n">
@@ -8179,13 +8191,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8212,7 +8224,7 @@
       <c r="I20" t="n">
         <v>5.609999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="K20" t="n">
@@ -8225,13 +8237,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8258,7 +8270,7 @@
       <c r="I21" t="n">
         <v>5.61</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="K21" t="n">
@@ -8271,13 +8283,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8304,7 +8316,7 @@
       <c r="I22" t="n">
         <v>5.53</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="K22" t="n">
@@ -8317,13 +8329,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8350,7 +8362,7 @@
       <c r="I23" t="n">
         <v>5.6</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="K23" t="n">
@@ -8363,13 +8375,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8396,7 +8408,7 @@
       <c r="I24" t="n">
         <v>5.66</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="K24" t="n">
@@ -8409,13 +8421,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8442,7 +8454,7 @@
       <c r="I25" t="n">
         <v>5.87</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="K25" t="n">
@@ -8455,13 +8467,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8488,7 +8500,7 @@
       <c r="I26" t="n">
         <v>6.08</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="K26" t="n">
@@ -8501,13 +8513,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8534,7 +8546,7 @@
       <c r="I27" t="n">
         <v>6.17</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="K27" t="n">
@@ -8547,13 +8559,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8580,7 +8592,7 @@
       <c r="I28" t="n">
         <v>6.3</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="K28" t="n">
@@ -8593,13 +8605,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8626,7 +8638,7 @@
       <c r="I29" t="n">
         <v>5.74</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="K29" t="n">
@@ -8639,13 +8651,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8672,7 +8684,7 @@
       <c r="I30" t="n">
         <v>5.66</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="K30" t="n">
@@ -8685,13 +8697,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8718,7 +8730,7 @@
       <c r="I31" t="n">
         <v>5.140000000000001</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="K31" t="n">
@@ -8731,13 +8743,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8764,7 +8776,7 @@
       <c r="I32" t="n">
         <v>4.92</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="K32" t="n">
@@ -8777,13 +8789,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8810,7 +8822,7 @@
       <c r="I33" t="n">
         <v>5.359999999999999</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="K33" t="n">
@@ -8823,13 +8835,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8856,7 +8868,7 @@
       <c r="I34" t="n">
         <v>5.17</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="K34" t="n">
@@ -8869,13 +8881,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8902,7 +8914,7 @@
       <c r="I35" t="n">
         <v>5.499999999999999</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="K35" t="n">
@@ -8915,13 +8927,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8948,7 +8960,7 @@
       <c r="I36" t="n">
         <v>5.279999999999999</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="K36" t="n">
@@ -8961,13 +8973,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8994,7 +9006,7 @@
       <c r="I37" t="n">
         <v>5.22</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="K37" t="n">
@@ -9007,13 +9019,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -9040,7 +9052,7 @@
       <c r="I38" t="n">
         <v>5.33</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K38" t="n">
@@ -9053,13 +9065,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9086,7 +9098,7 @@
       <c r="I39" t="n">
         <v>5.35</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="K39" t="n">
@@ -9099,13 +9111,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9132,7 +9144,7 @@
       <c r="I40" t="n">
         <v>5.62</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K40" t="n">
@@ -9145,13 +9157,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9178,7 +9190,7 @@
       <c r="I41" t="n">
         <v>4.32</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="K41" t="n">
@@ -9191,13 +9203,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9224,7 +9236,7 @@
       <c r="I42" t="n">
         <v>4.56</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K42" t="n">
@@ -9237,13 +9249,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9270,7 +9282,7 @@
       <c r="I43" t="n">
         <v>4.8</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="K43" t="n">
@@ -9283,13 +9295,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43542</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9316,7 +9328,7 @@
       <c r="I44" t="n">
         <v>3.3343783090291</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43542</v>
       </c>
       <c r="K44" t="n">
@@ -9329,13 +9341,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43542</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9362,7 +9374,7 @@
       <c r="I45" t="n">
         <v>9.682146930952552</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43542</v>
       </c>
       <c r="K45" t="n">
@@ -9375,13 +9387,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9408,7 +9420,7 @@
       <c r="I46" t="n">
         <v>9.032146930952552</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="K46" t="n">
@@ -9421,13 +9433,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9454,7 +9466,7 @@
       <c r="I47" t="n">
         <v>8.342146930952552</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="K47" t="n">
@@ -9467,13 +9479,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43781</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9500,7 +9512,7 @@
       <c r="I48" t="n">
         <v>9.707768621923451</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43781</v>
       </c>
       <c r="K48" t="n">
@@ -9513,13 +9525,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9546,7 +9558,7 @@
       <c r="I49" t="n">
         <v>4.19</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="K49" t="n">
@@ -9559,13 +9571,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9592,7 +9604,7 @@
       <c r="I50" t="n">
         <v>4.32</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="K50" t="n">
@@ -9605,13 +9617,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9638,7 +9650,7 @@
       <c r="I51" t="n">
         <v>4.23</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="K51" t="n">
@@ -9651,13 +9663,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9684,7 +9696,7 @@
       <c r="I52" t="n">
         <v>4.200000000000001</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K52" t="n">
@@ -9697,13 +9709,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9730,7 +9742,7 @@
       <c r="I53" t="n">
         <v>4.710000000000001</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="K53" t="n">
@@ -9743,13 +9755,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9776,7 +9788,7 @@
       <c r="I54" t="n">
         <v>5.5</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K54" t="n">
@@ -9789,13 +9801,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9822,7 +9834,7 @@
       <c r="I55" t="n">
         <v>6.23</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="K55" t="n">
@@ -9835,13 +9847,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9868,7 +9880,7 @@
       <c r="I56" t="n">
         <v>6.79</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="K56" t="n">
@@ -9881,13 +9893,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9914,7 +9926,7 @@
       <c r="I57" t="n">
         <v>7.33</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="K57" t="n">
@@ -9927,13 +9939,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44683</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9960,7 +9972,7 @@
       <c r="I58" t="n">
         <v>7.77</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44683</v>
       </c>
       <c r="K58" t="n">
@@ -9973,13 +9985,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -10006,7 +10018,7 @@
       <c r="I59" t="n">
         <v>6.91</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="K59" t="n">
@@ -10019,13 +10031,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -10052,7 +10064,7 @@
       <c r="I60" t="n">
         <v>7.57</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="K60" t="n">
@@ -10065,13 +10077,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10098,7 +10110,7 @@
       <c r="I61" t="n">
         <v>8.23</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="K61" t="n">
@@ -10111,13 +10123,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10144,7 +10156,7 @@
       <c r="I62" t="n">
         <v>8.99</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="K62" t="n">
@@ -10157,13 +10169,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10190,7 +10202,7 @@
       <c r="I63" t="n">
         <v>11.44</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="K63" t="n">
@@ -10203,13 +10215,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10236,7 +10248,7 @@
       <c r="I64" t="n">
         <v>12.09</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="K64" t="n">
@@ -10249,13 +10261,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10282,7 +10294,7 @@
       <c r="I65" t="n">
         <v>12.59</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="K65" t="n">
@@ -10295,13 +10307,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10328,7 +10340,7 @@
       <c r="I66" t="n">
         <v>12.88</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K66" t="n">
@@ -10341,13 +10353,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10374,7 +10386,7 @@
       <c r="I67" t="n">
         <v>13.13</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="K67" t="n">
@@ -10387,13 +10399,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10420,7 +10432,7 @@
       <c r="I68" t="n">
         <v>13.16</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K68" t="n">
@@ -10433,13 +10445,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10466,7 +10478,7 @@
       <c r="I69" t="n">
         <v>13.62</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="K69" t="n">
@@ -10479,13 +10491,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10512,7 +10524,7 @@
       <c r="I70" t="n">
         <v>13.78</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="K70" t="n">
@@ -10525,13 +10537,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10558,7 +10570,7 @@
       <c r="I71" t="n">
         <v>14.07</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K71" t="n">
@@ -10571,13 +10583,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10604,7 +10616,7 @@
       <c r="I72" t="n">
         <v>14.94</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="K72" t="n">
@@ -10617,13 +10629,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10650,7 +10662,7 @@
       <c r="I73" t="n">
         <v>14.61</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="K73" t="n">
@@ -10663,13 +10675,13 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B74" s="1" t="n">
+      <c r="B74" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C74" s="1" t="n">
+      <c r="C74" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D74" t="inlineStr">
@@ -10696,7 +10708,7 @@
       <c r="I74" t="n">
         <v>15.08</v>
       </c>
-      <c r="J74" s="1" t="n">
+      <c r="J74" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K74" t="n">
@@ -10709,13 +10721,13 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B75" s="1" t="n">
+      <c r="B75" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C75" s="1" t="n">
+      <c r="C75" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="D75" t="inlineStr">
@@ -10742,7 +10754,7 @@
       <c r="I75" t="n">
         <v>15.5</v>
       </c>
-      <c r="J75" s="1" t="n">
+      <c r="J75" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="K75" t="n">
@@ -10779,52 +10791,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39932</v>
       </c>
       <c r="C2" t="n">
@@ -10853,10 +10865,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40023</v>
       </c>
       <c r="C3" t="n">
@@ -10885,10 +10897,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40114</v>
       </c>
       <c r="C4" t="n">
@@ -10917,10 +10929,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40209</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40233</v>
       </c>
       <c r="C5" t="n">
@@ -10949,10 +10961,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40296</v>
       </c>
       <c r="C6" t="n">
@@ -10981,10 +10993,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="C7" t="n">
@@ -11013,10 +11025,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40478</v>
       </c>
       <c r="C8" t="n">
@@ -11045,10 +11057,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40574</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40597</v>
       </c>
       <c r="C9" t="n">
@@ -11077,10 +11089,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40660</v>
       </c>
       <c r="C10" t="n">
@@ -11109,10 +11121,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40751</v>
       </c>
       <c r="C11" t="n">
@@ -11141,10 +11153,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40842</v>
       </c>
       <c r="C12" t="n">
@@ -11173,10 +11185,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40939</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="C13" t="n">
@@ -11205,10 +11217,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41024</v>
       </c>
       <c r="C14" t="n">
@@ -11237,10 +11249,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C15" t="n">
@@ -11269,10 +11281,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C16" t="n">
@@ -11301,10 +11313,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41305</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41332</v>
       </c>
       <c r="C17" t="n">
@@ -11333,10 +11345,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41388</v>
       </c>
       <c r="C18" t="n">
@@ -11365,10 +11377,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41479</v>
       </c>
       <c r="C19" t="n">
@@ -11397,10 +11409,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41577</v>
       </c>
       <c r="C20" t="n">
@@ -11429,10 +11441,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41695</v>
       </c>
       <c r="C21" t="n">
@@ -11461,10 +11473,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41752</v>
       </c>
       <c r="C22" t="n">
@@ -11493,10 +11505,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41843</v>
       </c>
       <c r="C23" t="n">
@@ -11525,10 +11537,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41941</v>
       </c>
       <c r="C24" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42035</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42060</v>
       </c>
       <c r="C25" t="n">
@@ -11589,10 +11601,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42123</v>
       </c>
       <c r="C26" t="n">
@@ -11621,10 +11633,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42214</v>
       </c>
       <c r="C27" t="n">
@@ -11653,10 +11665,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42306</v>
       </c>
       <c r="C28" t="n">
@@ -11685,10 +11697,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42400</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42424</v>
       </c>
       <c r="C29" t="n">
@@ -11717,10 +11729,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42489</v>
       </c>
       <c r="C30" t="n">
@@ -11749,10 +11761,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42579</v>
       </c>
       <c r="C31" t="n">
@@ -11781,10 +11793,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42670</v>
       </c>
       <c r="C32" t="n">
@@ -11813,10 +11825,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42766</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42795</v>
       </c>
       <c r="C33" t="n">
@@ -11845,10 +11857,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C34" t="n">
@@ -11877,10 +11889,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42943</v>
       </c>
       <c r="C35" t="n">
@@ -11909,10 +11921,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C36" t="n">
@@ -11941,10 +11953,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43131</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="C37" t="n">
@@ -11973,10 +11985,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C38" t="n">
@@ -12005,10 +12017,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43307</v>
       </c>
       <c r="C39" t="n">
@@ -12037,10 +12049,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43413</v>
       </c>
       <c r="C40" t="n">
@@ -12069,10 +12081,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43524</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43542</v>
       </c>
       <c r="C41" t="n">
@@ -12101,10 +12113,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43585</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="C42" t="n">
@@ -12133,10 +12145,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43677</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43686</v>
       </c>
       <c r="C43" t="n">
@@ -12165,10 +12177,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43769</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43781</v>
       </c>
       <c r="C44" t="n">
@@ -12197,10 +12209,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43892</v>
       </c>
       <c r="C45" t="n">
@@ -12229,10 +12241,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43951</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43958</v>
       </c>
       <c r="C46" t="n">
@@ -12261,10 +12273,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="C47" t="n">
@@ -12293,10 +12305,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C48" t="n">
@@ -12325,10 +12337,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44227</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44256</v>
       </c>
       <c r="C49" t="n">
@@ -12357,10 +12369,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C50" t="n">
@@ -12389,10 +12401,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44407</v>
       </c>
       <c r="C51" t="n">
@@ -12421,10 +12433,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44498</v>
       </c>
       <c r="C52" t="n">
@@ -12453,10 +12465,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44592</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="C53" t="n">
@@ -12485,10 +12497,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44683</v>
       </c>
       <c r="C54" t="n">
@@ -12517,10 +12529,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44770</v>
       </c>
       <c r="C55" t="n">
@@ -12549,10 +12561,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44861</v>
       </c>
       <c r="C56" t="n">
@@ -12581,10 +12593,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44957</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="C57" t="n">
@@ -12613,10 +12625,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45043</v>
       </c>
       <c r="C58" t="n">
@@ -12645,10 +12657,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45134</v>
       </c>
       <c r="C59" t="n">
@@ -12677,10 +12689,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45225</v>
       </c>
       <c r="C60" t="n">
@@ -12709,10 +12721,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45322</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45350</v>
       </c>
       <c r="C61" t="n">
@@ -12741,10 +12753,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C62" t="n">
@@ -12773,10 +12785,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45506</v>
       </c>
       <c r="C63" t="n">
@@ -12805,10 +12817,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C64" t="n">
@@ -12837,10 +12849,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45714</v>
       </c>
       <c r="C65" t="n">
@@ -12869,10 +12881,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45778</v>
       </c>
       <c r="C66" t="n">
@@ -12901,10 +12913,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C67" t="n">
@@ -12933,10 +12945,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C68" t="n">
@@ -12965,10 +12977,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46053</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46078</v>
       </c>
       <c r="C69" t="n">
@@ -12997,10 +13009,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C70" t="n">
@@ -13029,10 +13041,10 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="C71" t="n">
@@ -13079,12 +13091,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/LIN.xlsx
+++ b/salidas/empresas/LIN.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>35.67365264892578</v>
+        <v>35.67364120483398</v>
       </c>
       <c r="C2" t="n">
         <v>52.68000030517578</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>36.55399703979492</v>
+        <v>36.55398559570312</v>
       </c>
       <c r="C3" t="n">
         <v>53.97999954223633</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>37.51774978637695</v>
+        <v>37.51778411865234</v>
       </c>
       <c r="C4" t="n">
         <v>55.15000152587891</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>38.18444442749023</v>
+        <v>38.18442535400391</v>
       </c>
       <c r="C5" t="n">
         <v>56.13000106811523</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>36.90210342407227</v>
+        <v>36.90209579467773</v>
       </c>
       <c r="C7" t="n">
         <v>54</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>37.47613525390625</v>
+        <v>37.47613906860352</v>
       </c>
       <c r="C8" t="n">
         <v>54.84000015258789</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>40.60362243652344</v>
+        <v>40.60363006591797</v>
       </c>
       <c r="C10" t="n">
         <v>59.15999984741211</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>42.82735061645508</v>
+        <v>42.82733917236328</v>
       </c>
       <c r="C12" t="n">
         <v>62.40000152587891</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>40.88278961181641</v>
+        <v>40.88278579711914</v>
       </c>
       <c r="C13" t="n">
         <v>59.33000183105469</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>42.50899887084961</v>
+        <v>42.50899505615234</v>
       </c>
       <c r="C15" t="n">
         <v>61.68999862670898</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>43.60012054443359</v>
+        <v>43.60009002685547</v>
       </c>
       <c r="C16" t="n">
         <v>62.95999908447266</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>44.70120239257812</v>
+        <v>44.70121383666992</v>
       </c>
       <c r="C17" t="n">
         <v>64.55000305175781</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>47.15266418457031</v>
+        <v>47.15266036987305</v>
       </c>
       <c r="C18" t="n">
         <v>68.08999633789062</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>50.07001495361328</v>
+        <v>50.07002258300781</v>
       </c>
       <c r="C19" t="n">
         <v>71.98999786376953</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>53.29027557373047</v>
+        <v>53.29027938842773</v>
       </c>
       <c r="C20" t="n">
         <v>76.62000274658203</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>58.48827743530273</v>
+        <v>58.48830795288086</v>
       </c>
       <c r="C22" t="n">
         <v>83.76000213623047</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>59.68934631347656</v>
+        <v>59.6893424987793</v>
       </c>
       <c r="C23" t="n">
         <v>85.48000335693359</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>62.16388702392578</v>
+        <v>62.16389465332031</v>
       </c>
       <c r="C25" t="n">
         <v>88.70999908447266</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>56.55085754394531</v>
+        <v>56.55084228515625</v>
       </c>
       <c r="C26" t="n">
         <v>80.69999694824219</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>56.25653076171875</v>
+        <v>56.25653839111328</v>
       </c>
       <c r="C27" t="n">
         <v>80.27999877929688</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>59.30306625366211</v>
+        <v>59.3030891418457</v>
       </c>
       <c r="C28" t="n">
         <v>84.23000335693359</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>64.28783416748047</v>
+        <v>64.28781890869141</v>
       </c>
       <c r="C29" t="n">
         <v>91.30999755859375</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>66.9281005859375</v>
+        <v>66.92806243896484</v>
       </c>
       <c r="C30" t="n">
         <v>95.05999755859375</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>66.61248016357422</v>
+        <v>66.61253356933594</v>
       </c>
       <c r="C31" t="n">
         <v>94.23999786376953</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>66.25205230712891</v>
+        <v>66.25199127197266</v>
       </c>
       <c r="C32" t="n">
         <v>93.73000335693359</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>63.50240325927734</v>
+        <v>63.50238418579102</v>
       </c>
       <c r="C33" t="n">
         <v>89.83999633789062</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>50.92344284057617</v>
+        <v>50.92346954345703</v>
       </c>
       <c r="C34" t="n">
         <v>71.73999786376953</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>46.24563980102539</v>
+        <v>46.24564361572266</v>
       </c>
       <c r="C35" t="n">
         <v>65.15000152587891</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>41.91566848754883</v>
+        <v>41.91567993164062</v>
       </c>
       <c r="C36" t="n">
         <v>59.04999923706055</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>44.49662017822266</v>
+        <v>44.49663162231445</v>
       </c>
       <c r="C38" t="n">
         <v>62.2599983215332</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>48.44217300415039</v>
+        <v>48.44216918945312</v>
       </c>
       <c r="C40" t="n">
         <v>67.29000091552734</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>53.71185302734375</v>
+        <v>53.71185684204102</v>
       </c>
       <c r="C41" t="n">
         <v>74.61000061035156</v>
@@ -1264,7 +1264,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>52.69676971435547</v>
+        <v>52.69678497314453</v>
       </c>
       <c r="C42" t="n">
         <v>73.19999694824219</v>
@@ -1289,7 +1289,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>51.4313850402832</v>
+        <v>51.43136978149414</v>
       </c>
       <c r="C43" t="n">
         <v>71.06999969482422</v>
@@ -1314,7 +1314,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>56.57667922973633</v>
+        <v>56.5766716003418</v>
       </c>
       <c r="C44" t="n">
         <v>78.18000030517578</v>
@@ -1339,7 +1339,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>55.44776916503906</v>
+        <v>55.44773864746094</v>
       </c>
       <c r="C45" t="n">
         <v>76.62000274658203</v>
@@ -1364,7 +1364,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>59.4317741394043</v>
+        <v>59.43177032470703</v>
       </c>
       <c r="C46" t="n">
         <v>81.69000244140625</v>
@@ -1389,7 +1389,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>57.7948112487793</v>
+        <v>57.79482269287109</v>
       </c>
       <c r="C47" t="n">
         <v>79.44000244140625</v>
@@ -1414,7 +1414,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>59.67911148071289</v>
+        <v>59.67913436889648</v>
       </c>
       <c r="C48" t="n">
         <v>82.02999877929688</v>
@@ -1439,7 +1439,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>58.71167755126953</v>
+        <v>58.71171188354492</v>
       </c>
       <c r="C49" t="n">
         <v>80.30999755859375</v>
@@ -1489,7 +1489,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>54.93207168579102</v>
+        <v>54.93207931518555</v>
       </c>
       <c r="C51" t="n">
         <v>75.13999938964844</v>
@@ -1518,7 +1518,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>61.03508377075195</v>
+        <v>61.03508758544922</v>
       </c>
       <c r="C52" t="n">
         <v>83</v>
@@ -1547,7 +1547,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>61.60128021240234</v>
+        <v>61.60129547119141</v>
       </c>
       <c r="C53" t="n">
         <v>83.76999664306641</v>
@@ -1576,7 +1576,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>57.06410980224609</v>
+        <v>57.06412887573242</v>
       </c>
       <c r="C54" t="n">
         <v>77.59999847412109</v>
@@ -1605,7 +1605,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>56.20429229736328</v>
+        <v>56.20426940917969</v>
       </c>
       <c r="C55" t="n">
         <v>75.98999786376953</v>
@@ -1634,7 +1634,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>64.21440124511719</v>
+        <v>64.21443176269531</v>
       </c>
       <c r="C56" t="n">
         <v>86.81999969482422</v>
@@ -1663,7 +1663,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>63.63013458251953</v>
+        <v>63.63012313842773</v>
       </c>
       <c r="C57" t="n">
         <v>86.02999877929688</v>
@@ -1692,7 +1692,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>67.10546112060547</v>
+        <v>67.10544586181641</v>
       </c>
       <c r="C58" t="n">
         <v>90.26000213623047</v>
@@ -1721,7 +1721,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>67.90838623046875</v>
+        <v>67.90840148925781</v>
       </c>
       <c r="C59" t="n">
         <v>91.33999633789062</v>
@@ -1750,7 +1750,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>68.43627166748047</v>
+        <v>68.43629455566406</v>
       </c>
       <c r="C60" t="n">
         <v>92.05000305175781</v>
@@ -1779,7 +1779,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>71.31880187988281</v>
+        <v>71.31878662109375</v>
       </c>
       <c r="C61" t="n">
         <v>95.47000122070312</v>
@@ -1808,7 +1808,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>69.50351715087891</v>
+        <v>69.50350189208984</v>
       </c>
       <c r="C62" t="n">
         <v>93.04000091552734</v>
@@ -1837,7 +1837,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>74.23967742919922</v>
+        <v>74.23966979980469</v>
       </c>
       <c r="C63" t="n">
         <v>99.37999725341797</v>
@@ -1866,7 +1866,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>76.28736877441406</v>
+        <v>76.28738403320312</v>
       </c>
       <c r="C64" t="n">
         <v>101.5999984741211</v>
@@ -1895,7 +1895,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>79.90652465820312</v>
+        <v>79.90650177001953</v>
       </c>
       <c r="C65" t="n">
         <v>106.4199981689453</v>
@@ -1924,7 +1924,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>79.47103881835938</v>
+        <v>79.47101593017578</v>
       </c>
       <c r="C66" t="n">
         <v>105.8399963378906</v>
@@ -1953,7 +1953,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>81.78216552734375</v>
+        <v>81.78214263916016</v>
       </c>
       <c r="C67" t="n">
         <v>108.3899993896484</v>
@@ -2011,7 +2011,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>74.31242370605469</v>
+        <v>74.31240081787109</v>
       </c>
       <c r="C69" t="n">
         <v>98.48999786376953</v>
@@ -2040,7 +2040,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>70.89331817626953</v>
+        <v>70.89328002929688</v>
       </c>
       <c r="C70" t="n">
         <v>93.48000335693359</v>
@@ -2069,7 +2069,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>77.10443115234375</v>
+        <v>77.10440826416016</v>
       </c>
       <c r="C71" t="n">
         <v>101.6699981689453</v>
@@ -2098,7 +2098,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>77.35469818115234</v>
+        <v>77.35468292236328</v>
       </c>
       <c r="C72" t="n">
         <v>102</v>
@@ -2127,7 +2127,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>81.47624969482422</v>
+        <v>81.47623443603516</v>
       </c>
       <c r="C73" t="n">
         <v>106.9000015258789</v>
@@ -2156,7 +2156,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>80.94271087646484</v>
+        <v>80.94273376464844</v>
       </c>
       <c r="C74" t="n">
         <v>106.1999969482422</v>
@@ -2185,7 +2185,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>83.07682800292969</v>
+        <v>83.07681274414062</v>
       </c>
       <c r="C75" t="n">
         <v>109</v>
@@ -2214,7 +2214,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>87.81576538085938</v>
+        <v>87.81574249267578</v>
       </c>
       <c r="C76" t="n">
         <v>114.6399993896484</v>
@@ -2243,7 +2243,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>88.62770843505859</v>
+        <v>88.62769317626953</v>
       </c>
       <c r="C77" t="n">
         <v>115.6999969482422</v>
@@ -2272,7 +2272,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>81.38124847412109</v>
+        <v>81.38123321533203</v>
       </c>
       <c r="C78" t="n">
         <v>106.2399978637695</v>
@@ -2330,7 +2330,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>79.90415954589844</v>
+        <v>79.90419006347656</v>
       </c>
       <c r="C80" t="n">
         <v>103.7600021362305</v>
@@ -2388,7 +2388,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>80.42095947265625</v>
+        <v>80.42096710205078</v>
       </c>
       <c r="C82" t="n">
         <v>103.879997253418</v>
@@ -2417,7 +2417,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>82.22475433349609</v>
+        <v>82.22476959228516</v>
       </c>
       <c r="C83" t="n">
         <v>106.2099990844727</v>
@@ -2475,7 +2475,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>85.17626953125</v>
+        <v>85.17625427246094</v>
       </c>
       <c r="C85" t="n">
         <v>109.4499969482422</v>
@@ -2504,7 +2504,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>85.89223480224609</v>
+        <v>85.89220428466797</v>
       </c>
       <c r="C86" t="n">
         <v>110.370002746582</v>
@@ -2533,7 +2533,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>87.97786712646484</v>
+        <v>87.97784423828125</v>
       </c>
       <c r="C87" t="n">
         <v>113.0500030517578</v>
@@ -2591,7 +2591,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>89.42587280273438</v>
+        <v>89.42588043212891</v>
       </c>
       <c r="C89" t="n">
         <v>114.3000030517578</v>
@@ -2620,7 +2620,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>89.44934844970703</v>
+        <v>89.44932556152344</v>
       </c>
       <c r="C90" t="n">
         <v>114.3300018310547</v>
@@ -2649,7 +2649,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>90.56449890136719</v>
+        <v>90.56451416015625</v>
       </c>
       <c r="C91" t="n">
         <v>115.1600036621094</v>
@@ -2794,7 +2794,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>99.80355834960938</v>
+        <v>99.80357360839844</v>
       </c>
       <c r="C96" t="n">
         <v>126.2600021362305</v>
@@ -2823,7 +2823,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>103.2823715209961</v>
+        <v>103.282356262207</v>
       </c>
       <c r="C97" t="n">
         <v>130.0299987792969</v>
@@ -2881,7 +2881,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>103.5524368286133</v>
+        <v>103.5524215698242</v>
       </c>
       <c r="C99" t="n">
         <v>130.3699951171875</v>
@@ -2910,7 +2910,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>104.5477676391602</v>
+        <v>104.5477752685547</v>
       </c>
       <c r="C100" t="n">
         <v>130.9700012207031</v>
@@ -2939,7 +2939,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>104.212516784668</v>
+        <v>104.2124938964844</v>
       </c>
       <c r="C101" t="n">
         <v>130.5500030517578</v>
@@ -2968,7 +2968,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>105.5615463256836</v>
+        <v>105.5615615844727</v>
       </c>
       <c r="C102" t="n">
         <v>132.2400054931641</v>
@@ -2997,7 +2997,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>106.5586395263672</v>
+        <v>106.5586318969727</v>
       </c>
       <c r="C103" t="n">
         <v>132.8399963378906</v>
@@ -3026,7 +3026,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>102.7884979248047</v>
+        <v>102.7884902954102</v>
       </c>
       <c r="C104" t="n">
         <v>128.1399993896484</v>
@@ -3055,7 +3055,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>105.5238723754883</v>
+        <v>105.5238647460938</v>
       </c>
       <c r="C105" t="n">
         <v>131.5500030517578</v>
@@ -3084,7 +3084,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>103.9895401000977</v>
+        <v>103.989501953125</v>
       </c>
       <c r="C106" t="n">
         <v>129</v>
@@ -3171,7 +3171,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>104.9721603393555</v>
+        <v>104.9721374511719</v>
       </c>
       <c r="C109" t="n">
         <v>129.5599975585938</v>
@@ -3200,7 +3200,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>97.70446014404297</v>
+        <v>97.70447540283203</v>
       </c>
       <c r="C110" t="n">
         <v>120.5899963378906</v>
@@ -3258,7 +3258,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>98.37107086181641</v>
+        <v>98.37104797363281</v>
       </c>
       <c r="C112" t="n">
         <v>120.7399978637695</v>
@@ -3287,7 +3287,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>99.34059143066406</v>
+        <v>99.34058380126953</v>
       </c>
       <c r="C113" t="n">
         <v>121.9300003051758</v>
@@ -3316,7 +3316,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>100.0982513427734</v>
+        <v>100.098274230957</v>
       </c>
       <c r="C114" t="n">
         <v>122.8600006103516</v>
@@ -3345,7 +3345,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>97.97319030761719</v>
+        <v>97.97315216064453</v>
       </c>
       <c r="C115" t="n">
         <v>119.5500030517578</v>
@@ -3374,7 +3374,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>93.53959655761719</v>
+        <v>93.53957366943359</v>
       </c>
       <c r="C116" t="n">
         <v>114.1399993896484</v>
@@ -3432,7 +3432,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>84.05970764160156</v>
+        <v>84.05974578857422</v>
       </c>
       <c r="C118" t="n">
         <v>101.8600006103516</v>
@@ -3461,7 +3461,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>91.67676544189453</v>
+        <v>91.67678070068359</v>
       </c>
       <c r="C119" t="n">
         <v>111.0899963378906</v>
@@ -3519,7 +3519,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>85.05638885498047</v>
+        <v>85.05641174316406</v>
       </c>
       <c r="C121" t="n">
         <v>102.4000015258789</v>
@@ -3548,7 +3548,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>83.06291198730469</v>
+        <v>83.06291961669922</v>
       </c>
       <c r="C122" t="n">
         <v>100</v>
@@ -3577,7 +3577,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>84.54975128173828</v>
+        <v>84.54971313476562</v>
       </c>
       <c r="C123" t="n">
         <v>101.7900009155273</v>
@@ -3606,7 +3606,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>95.75513458251953</v>
+        <v>95.75508880615234</v>
       </c>
       <c r="C124" t="n">
         <v>114.4499969482422</v>
@@ -3635,7 +3635,7 @@
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>98.27346038818359</v>
+        <v>98.27344512939453</v>
       </c>
       <c r="C125" t="n">
         <v>117.4599990844727</v>
@@ -3664,7 +3664,7 @@
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>91.91485595703125</v>
+        <v>91.91486358642578</v>
       </c>
       <c r="C126" t="n">
         <v>109.8600006103516</v>
@@ -3693,7 +3693,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>94.67385101318359</v>
+        <v>94.673828125</v>
       </c>
       <c r="C127" t="n">
         <v>112.3899993896484</v>
@@ -3751,7 +3751,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>102.8026885986328</v>
+        <v>102.8026962280273</v>
       </c>
       <c r="C129" t="n">
         <v>122.0400009155273</v>
@@ -3780,7 +3780,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>102.4056396484375</v>
+        <v>102.4056243896484</v>
       </c>
       <c r="C130" t="n">
         <v>120.8300018310547</v>
@@ -3809,7 +3809,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>99.21047973632812</v>
+        <v>99.21046447753906</v>
       </c>
       <c r="C131" t="n">
         <v>117.0599975585938</v>
@@ -3867,7 +3867,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>99.947509765625</v>
+        <v>99.94752502441406</v>
       </c>
       <c r="C133" t="n">
         <v>117.1900024414062</v>
@@ -3896,7 +3896,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>101.0136337280273</v>
+        <v>101.0136184692383</v>
       </c>
       <c r="C134" t="n">
         <v>118.4400024414062</v>
@@ -3925,7 +3925,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>101.2438735961914</v>
+        <v>101.2438659667969</v>
       </c>
       <c r="C135" t="n">
         <v>118.7099990844727</v>
@@ -3954,7 +3954,7 @@
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>101.8255996704102</v>
+        <v>101.8255767822266</v>
       </c>
       <c r="C136" t="n">
         <v>118.5999984741211</v>
@@ -3983,7 +3983,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>107.3032379150391</v>
+        <v>107.3032302856445</v>
       </c>
       <c r="C137" t="n">
         <v>124.9800033569336</v>
@@ -4012,7 +4012,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>113.5793380737305</v>
+        <v>113.5793075561523</v>
       </c>
       <c r="C138" t="n">
         <v>132.2899932861328</v>
@@ -4041,7 +4041,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>114.4627685546875</v>
+        <v>114.462776184082</v>
       </c>
       <c r="C139" t="n">
         <v>132.5500030517578</v>
@@ -4070,7 +4070,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>112.3989028930664</v>
+        <v>112.3988876342773</v>
       </c>
       <c r="C140" t="n">
         <v>130.1600036621094</v>
@@ -4128,7 +4128,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>121.3975982666016</v>
+        <v>121.3976287841797</v>
       </c>
       <c r="C142" t="n">
         <v>139.7400054931641</v>
@@ -4157,7 +4157,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>126.9401550292969</v>
+        <v>126.9401931762695</v>
       </c>
       <c r="C143" t="n">
         <v>146.1199951171875</v>
@@ -4244,7 +4244,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>141.0185546875</v>
+        <v>141.0185852050781</v>
       </c>
       <c r="C146" t="n">
         <v>161.4900054931641</v>
@@ -4302,7 +4302,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>126.692008972168</v>
+        <v>126.6919860839844</v>
       </c>
       <c r="C148" t="n">
         <v>144.3000030517578</v>
@@ -4331,7 +4331,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>133.908935546875</v>
+        <v>133.9090118408203</v>
       </c>
       <c r="C149" t="n">
         <v>152.5200042724609</v>
@@ -4360,7 +4360,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>137.1925659179688</v>
+        <v>137.1925506591797</v>
       </c>
       <c r="C150" t="n">
         <v>156.2599945068359</v>
@@ -4389,7 +4389,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>139.5738677978516</v>
+        <v>139.5738372802734</v>
       </c>
       <c r="C151" t="n">
         <v>158.1499938964844</v>
@@ -4418,7 +4418,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>147.8256378173828</v>
+        <v>147.8255920410156</v>
       </c>
       <c r="C152" t="n">
         <v>167.5</v>
@@ -4447,7 +4447,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>140.3153991699219</v>
+        <v>140.3153381347656</v>
       </c>
       <c r="C153" t="n">
         <v>158.1900024414062</v>
@@ -4534,7 +4534,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>141.0782012939453</v>
+        <v>141.0781860351562</v>
       </c>
       <c r="C156" t="n">
         <v>159.0500030517578</v>
@@ -4563,7 +4563,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>139.1397857666016</v>
+        <v>139.1398010253906</v>
       </c>
       <c r="C157" t="n">
         <v>156.0399932861328</v>
@@ -4592,7 +4592,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>145.3548278808594</v>
+        <v>145.3548583984375</v>
       </c>
       <c r="C158" t="n">
         <v>163.0099945068359</v>
@@ -4621,7 +4621,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>154.4769134521484</v>
+        <v>154.4768829345703</v>
       </c>
       <c r="C159" t="n">
         <v>173.2400054931641</v>
@@ -4650,7 +4650,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>157.6913757324219</v>
+        <v>157.69140625</v>
       </c>
       <c r="C160" t="n">
         <v>175.9299926757812</v>
@@ -4679,7 +4679,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>161.5724945068359</v>
+        <v>161.5724639892578</v>
       </c>
       <c r="C161" t="n">
         <v>180.2599945068359</v>
@@ -4708,7 +4708,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>162.608154296875</v>
+        <v>162.6082153320312</v>
       </c>
       <c r="C162" t="n">
         <v>180.5500030517578</v>
@@ -4737,7 +4737,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>180.8458709716797</v>
+        <v>180.8459167480469</v>
       </c>
       <c r="C163" t="n">
         <v>200.8000030517578</v>
@@ -4766,7 +4766,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>172.2719421386719</v>
+        <v>172.2719268798828</v>
       </c>
       <c r="C164" t="n">
         <v>191.2799987792969</v>
@@ -4795,7 +4795,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>170.9344482421875</v>
+        <v>170.9344177246094</v>
       </c>
       <c r="C165" t="n">
         <v>188.9100036621094</v>
@@ -4824,7 +4824,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>175.2867736816406</v>
+        <v>175.2867431640625</v>
       </c>
       <c r="C166" t="n">
         <v>193.7200012207031</v>
@@ -4853,7 +4853,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>179.4762573242188</v>
+        <v>179.4761962890625</v>
       </c>
       <c r="C167" t="n">
         <v>198.3500061035156</v>
@@ -4911,7 +4911,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>193.4626312255859</v>
+        <v>193.4626159667969</v>
       </c>
       <c r="C169" t="n">
         <v>212.8999938964844</v>
@@ -4940,7 +4940,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>184.5846405029297</v>
+        <v>184.5845642089844</v>
       </c>
       <c r="C170" t="n">
         <v>203.1300048828125</v>
@@ -4998,7 +4998,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>157.9454345703125</v>
+        <v>157.9454650878906</v>
       </c>
       <c r="C172" t="n">
         <v>173</v>
@@ -5056,7 +5056,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>184.7322998046875</v>
+        <v>184.7322845458984</v>
       </c>
       <c r="C174" t="n">
         <v>202.3399963378906</v>
@@ -5143,7 +5143,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>229.0825042724609</v>
+        <v>229.0824737548828</v>
       </c>
       <c r="C177" t="n">
         <v>249.7400054931641</v>
@@ -5172,7 +5172,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>219.2545776367188</v>
+        <v>219.2545623779297</v>
       </c>
       <c r="C178" t="n">
         <v>238.1300048828125</v>
@@ -5201,7 +5201,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>202.8746795654297</v>
+        <v>202.8746643066406</v>
       </c>
       <c r="C179" t="n">
         <v>220.3399963378906</v>
@@ -5259,7 +5259,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>243.5286254882812</v>
+        <v>243.5286560058594</v>
       </c>
       <c r="C181" t="n">
         <v>263.510009765625</v>
@@ -5288,7 +5288,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>226.7919158935547</v>
+        <v>226.7918853759766</v>
       </c>
       <c r="C182" t="n">
         <v>245.3999938964844</v>
@@ -5317,7 +5317,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>225.7475738525391</v>
+        <v>225.74755859375</v>
       </c>
       <c r="C183" t="n">
         <v>244.2700042724609</v>
@@ -5433,7 +5433,7 @@
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>269.2714538574219</v>
+        <v>269.271484375</v>
       </c>
       <c r="C187" t="n">
         <v>289.1000061035156</v>
@@ -5462,7 +5462,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>286.3070373535156</v>
+        <v>286.3070983886719</v>
       </c>
       <c r="C188" t="n">
         <v>307.3900146484375</v>
@@ -5491,7 +5491,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>293.01318359375</v>
+        <v>293.0131225585938</v>
       </c>
       <c r="C189" t="n">
         <v>314.5899963378906</v>
@@ -5520,7 +5520,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>274.1838684082031</v>
+        <v>274.1838073730469</v>
       </c>
       <c r="C190" t="n">
         <v>293.3800048828125</v>
@@ -5549,7 +5549,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>298.3144226074219</v>
+        <v>298.3144836425781</v>
       </c>
       <c r="C191" t="n">
         <v>319.2000122070312</v>
@@ -5607,7 +5607,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>324.8446044921875</v>
+        <v>324.8445129394531</v>
       </c>
       <c r="C193" t="n">
         <v>346.4299926757812</v>
@@ -5636,7 +5636,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>298.8235778808594</v>
+        <v>298.8236999511719</v>
       </c>
       <c r="C194" t="n">
         <v>318.6799926757812</v>
@@ -5665,7 +5665,7 @@
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>274.9687805175781</v>
+        <v>274.9688110351562</v>
       </c>
       <c r="C195" t="n">
         <v>293.239990234375</v>
@@ -5694,7 +5694,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>300.7286987304688</v>
+        <v>300.7286682128906</v>
       </c>
       <c r="C196" t="n">
         <v>319.4299926757812</v>
@@ -5752,7 +5752,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>305.6712951660156</v>
+        <v>305.67138671875</v>
       </c>
       <c r="C198" t="n">
         <v>324.6799926757812</v>
@@ -5781,7 +5781,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>271.6908569335938</v>
+        <v>271.69091796875</v>
       </c>
       <c r="C199" t="n">
         <v>287.5299987792969</v>
@@ -5810,7 +5810,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>285.3638610839844</v>
+        <v>285.3638000488281</v>
       </c>
       <c r="C200" t="n">
         <v>302</v>
@@ -5839,7 +5839,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>267.2781677246094</v>
+        <v>267.2781982421875</v>
       </c>
       <c r="C201" t="n">
         <v>282.8599853515625</v>
@@ -5868,7 +5868,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>255.7971343994141</v>
+        <v>255.7971954345703</v>
       </c>
       <c r="C202" t="n">
         <v>269.5899963378906</v>
@@ -5897,7 +5897,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>282.1369934082031</v>
+        <v>282.136962890625</v>
       </c>
       <c r="C203" t="n">
         <v>297.3500061035156</v>
@@ -5955,7 +5955,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>310.5719299316406</v>
+        <v>310.5718688964844</v>
       </c>
       <c r="C205" t="n">
         <v>326.1799926757812</v>
@@ -5984,7 +5984,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>315.1040954589844</v>
+        <v>315.1041259765625</v>
       </c>
       <c r="C206" t="n">
         <v>330.9400024414062</v>
@@ -6013,7 +6013,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>331.7000732421875</v>
+        <v>331.7000122070312</v>
       </c>
       <c r="C207" t="n">
         <v>348.3699951171875</v>
@@ -6129,7 +6129,7 @@
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>365.5222473144531</v>
+        <v>365.5221862792969</v>
       </c>
       <c r="C211" t="n">
         <v>381.0799865722656</v>
@@ -6158,7 +6158,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>374.7207641601562</v>
+        <v>374.7207336425781</v>
       </c>
       <c r="C212" t="n">
         <v>390.6700134277344</v>
@@ -6245,7 +6245,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>367.7696533203125</v>
+        <v>367.7696838378906</v>
       </c>
       <c r="C215" t="n">
         <v>382.1600036621094</v>
@@ -6332,7 +6332,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>390.7901611328125</v>
+        <v>390.7902221679688</v>
       </c>
       <c r="C218" t="n">
         <v>404.8299865722656</v>
@@ -6390,7 +6390,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>449.5423889160156</v>
+        <v>449.5424194335938</v>
       </c>
       <c r="C220" t="n">
         <v>464.3200073242188</v>
@@ -6419,7 +6419,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>426.9258117675781</v>
+        <v>426.9259033203125</v>
       </c>
       <c r="C221" t="n">
         <v>440.9599914550781</v>
@@ -6477,7 +6477,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>426.2082824707031</v>
+        <v>426.2083129882812</v>
       </c>
       <c r="C223" t="n">
         <v>438.8099975585938</v>
@@ -6506,7 +6506,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>440.4764404296875</v>
+        <v>440.4764709472656</v>
       </c>
       <c r="C224" t="n">
         <v>453.5</v>
@@ -6535,7 +6535,7 @@
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>464.5156860351562</v>
+        <v>464.5157165527344</v>
       </c>
       <c r="C225" t="n">
         <v>478.25</v>
@@ -6564,7 +6564,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>464.5276794433594</v>
+        <v>464.5276489257812</v>
       </c>
       <c r="C226" t="n">
         <v>476.8599853515625</v>
@@ -6593,7 +6593,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>444.3532409667969</v>
+        <v>444.353271484375</v>
       </c>
       <c r="C227" t="n">
         <v>456.1499938964844</v>
@@ -6622,7 +6622,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>449.0680847167969</v>
+        <v>449.068115234375</v>
       </c>
       <c r="C228" t="n">
         <v>460.989990234375</v>
@@ -6651,7 +6651,7 @@
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>409.0795593261719</v>
+        <v>409.0795288085938</v>
       </c>
       <c r="C229" t="n">
         <v>418.6700134277344</v>
@@ -6680,7 +6680,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>435.9006958007812</v>
+        <v>435.9007263183594</v>
       </c>
       <c r="C230" t="n">
         <v>446.1199951171875</v>
@@ -6738,7 +6738,7 @@
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>456.4913330078125</v>
+        <v>456.4912719726562</v>
       </c>
       <c r="C232" t="n">
         <v>465.6400146484375</v>
@@ -6825,7 +6825,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>461.4286804199219</v>
+        <v>461.4287109375</v>
       </c>
       <c r="C235" t="n">
         <v>469.1799926757812</v>
@@ -6854,7 +6854,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>452.6560974121094</v>
+        <v>452.6560668945312</v>
       </c>
       <c r="C236" t="n">
         <v>460.260009765625</v>
@@ -6912,7 +6912,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>468.6425476074219</v>
+        <v>468.6426086425781</v>
       </c>
       <c r="C238" t="n">
         <v>475</v>
@@ -6999,7 +6999,7 @@
         <v>46022</v>
       </c>
       <c r="B241" t="n">
-        <v>422.2324829101562</v>
+        <v>422.2325134277344</v>
       </c>
       <c r="C241" t="n">
         <v>426.3900146484375</v>
@@ -7086,7 +7086,7 @@
         <v>46112</v>
       </c>
       <c r="B244" t="n">
-        <v>492.5751342773438</v>
+        <v>492.5751037597656</v>
       </c>
       <c r="C244" t="n">
         <v>495.760009765625</v>
